--- a/backend/data/raw/dict_new.xlsx
+++ b/backend/data/raw/dict_new.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T97"/>
+  <dimension ref="A1:X97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="14.4"/>
   <cols>
     <col width="46.44140625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -567,6 +567,26 @@
           <t>add_indices_de</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>pretty_name_pt</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>dataset_pt</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>description_for_ui_pt</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>add_indices_pt</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -660,6 +680,26 @@
           <t xml:space="preserve"> Höhere Werte bedeuten höhere Ebenen subnationaler Demokratie.</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Índice SUR Giraudy (2015)</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Índices de Democracia</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>o nível de democracia subnacional</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Valores mais altos indicam maiores níveis de democracia subnacional.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -753,6 +793,26 @@
           <t xml:space="preserve"> Höhere Werte bedeuten höhere Ebenen subnationaler Demokratie.</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Índice SUR</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Índices de Democracia</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>o nível de democracia subnacional no poder executivo</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Valores mais altos indicam maiores níveis de democracia subnacional.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -846,6 +906,26 @@
           <t xml:space="preserve"> Höhere Werte bedeuten größeren exekutiven Parteienwettbewerb.</t>
         </is>
       </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Contestação Executiva</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Índices de Democracia</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>o nível de contestação subnacional executiva</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Valores mais altos indicam maiores níveis de competitividade executiva subnacional.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -939,6 +1019,26 @@
           <t xml:space="preserve"> Höhere Werte bedeuten größeren legislativen Parteienwettbewerb.</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Contestação Legislativa</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Índices de Democracia</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>o nível de contestação subnacional legislativa</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Valores mais altos indicam maiores níveis de competitividade legislativa subnacional.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1032,6 +1132,26 @@
           <t xml:space="preserve"> Höhere Werte bedeuten mehr exekutive Amtswechsel.</t>
         </is>
       </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Alternância Executiva</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Índices de Democracia</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>a média de alternância do governador e do partido</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Valores mais altos indicam maior alternância executiva subnacional.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1125,6 +1245,26 @@
           <t xml:space="preserve"> Höhere Werte bedeuten sauberere subnational-exekutive Wahlen.</t>
         </is>
       </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Eleições Limpas Giraudy (2015)</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Índices de Democracia</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>o índice de conflito pós-eleitoral</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Valores mais altos indicam eleições mais limpas no nível executivo subnacional, refletindo menor conflito pós-eleitoral.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1188,6 +1328,16 @@
           <t>Name des Landes</t>
         </is>
       </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>País</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>nome do país</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1251,6 +1401,16 @@
           <t>Kalenderjahr</t>
         </is>
       </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>ano calendário</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1329,6 +1489,21 @@
           <t>Name der subnationalen Einheit</t>
         </is>
       </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Executivo</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>nome da unidade subnacional</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1407,6 +1582,21 @@
           <t>geografische Region im Land</t>
         </is>
       </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Região</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Executivo</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>região geográfica dentro do país</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1470,6 +1660,16 @@
           <t>Name des Staatsoberhauptes</t>
         </is>
       </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nome do Presidente</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>nome do chefe de estado</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1538,6 +1738,16 @@
           <t>das Geschlecht des Staatsoberhauptes</t>
         </is>
       </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gênero do Presidente</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>o gênero do chefe de estado</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1611,6 +1821,16 @@
           <t>Anfangs- und Enddatum der Amtszeit des Präsidenten</t>
         </is>
       </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mandato do Presidente</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>datas de início e fim do mandato presidencial</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1679,6 +1899,16 @@
           <t>Gesamtdauer der Amtszeit des Präsidenten in Jahren</t>
         </is>
       </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Duração do Mandato Presidencial</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>duração total do mandato presidencial em anos</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1747,6 +1977,16 @@
           <t>ob der Präsident wiedergewählt wurde</t>
         </is>
       </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Reeleição Presidencial</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>se o presidente foi reeleito</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1815,6 +2055,16 @@
           <t>ob der Präsident das Amt vorzeitig verließ</t>
         </is>
       </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Saída Antecipada do Presidente</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>se o presidente deixou o cargo antes de completar o mandato</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1878,6 +2128,16 @@
           <t>politische Partei des Präsidenten</t>
         </is>
       </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Partido do Presidente</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>partido político do presidente</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1946,6 +2206,16 @@
           <t>ideologische Einordnung der Partei des Präsidenten</t>
         </is>
       </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ideologia do Partido Presidencial</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>classificação ideológica do partido do presidente</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2014,6 +2284,16 @@
           <t>ob Präsidentschaftswahlen stattfanden</t>
         </is>
       </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ano de Eleição Presidencial</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>se foram realizadas eleições presidenciais</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2092,6 +2372,21 @@
           <t>Name des Gouverneurskandidaten</t>
         </is>
       </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Nome do Governador</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Executivo</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>nome do candidato vencedor ao governo</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2175,6 +2470,21 @@
           <t>das Geschlecht des Gouverneurs</t>
         </is>
       </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gênero do Governador</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Executivo</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>o gênero do governador</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2248,6 +2558,16 @@
           <t>Anfangs- und Enddatum der Gouverneursamtszeit</t>
         </is>
       </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Mandato do Governador</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>datas de início e fim do mandato do governador</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2331,6 +2651,21 @@
           <t>ob ein Gouverneurswechsel stattfand</t>
         </is>
       </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Mudança de Governador</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Executivo</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>se ocorreu uma mudança de governador</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2414,6 +2749,21 @@
           <t>kumulierte Anzahl von Gouverneurswechseln</t>
         </is>
       </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Total de Mudanças de Governador</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Executivo</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>contagem acumulada de mudanças de governador</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2497,6 +2847,21 @@
           <t>Gesamtdauer der Gouverneursamtszeit in Jahren</t>
         </is>
       </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Duração do Mandato do Governador</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Executivo</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>duração total do mandato do governador em anos</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2580,6 +2945,21 @@
           <t>ob der Gouverneur vorzeitig zurücktrat</t>
         </is>
       </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Saída Antecipada do Governador</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Executivo</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>se o governador deixou o cargo antes do tempo</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2663,6 +3043,21 @@
           <t>ob der Gouverneur wiedergewählt wurde</t>
         </is>
       </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Reeleição do Governador</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Executivo</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>se o governador foi reeleito</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2746,6 +3141,21 @@
           <t>die Gesamtzahl der Jahre des Gouverneurs im Amt</t>
         </is>
       </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Anos do Governador no Cargo</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Executivo</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>o total de anos que o governador serviu em todos os mandatos</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2824,6 +3234,21 @@
           <t>die politische Partei des Gouverneurs</t>
         </is>
       </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Partido do Governador</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Executivo</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>o partido político do governador</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2907,6 +3332,21 @@
           <t>ob ein Parteiwechsel stattfand</t>
         </is>
       </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Mudança de Partido do Governador</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Executivo</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>se ocorreu uma mudança de partido</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2990,6 +3430,21 @@
           <t>kumulierte Anzahl von Parteiwechseln</t>
         </is>
       </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Total de Mudanças de Partido</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Executivo</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>contagem acumulada de mudanças de partido</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3073,6 +3528,21 @@
           <t>die kumulierten Jahre der Gouverneurspartei an der Macht</t>
         </is>
       </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Anos do Partido no Poder</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Executivo</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>os anos acumulados do partido do governador no poder</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3156,6 +3626,21 @@
           <t>die ideologische Einordnung der Gouverneurspartei</t>
         </is>
       </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ideologia do Partido do Governador</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Executivo</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>a classificação ideológica do partido do governador</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3234,6 +3719,16 @@
           <t>ob Gouverneurswahlen stattfanden</t>
         </is>
       </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ano de Eleição para Governador</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>se foram realizadas eleições para governador</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3317,6 +3812,21 @@
           <t>die effektive Anzahl der Parteien (Laakso &amp; Taagepera, 1979) im Exekutivbereich</t>
         </is>
       </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Número Efetivo de Partidos</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Eleições Executivas</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>o número efetivo de partidos (Laakso e Taagepera, 1979) no Executivo</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3400,6 +3910,21 @@
           <t>kumulierte Anzahl von Gouverneurswahlen</t>
         </is>
       </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Eleições Acumuladas Exec.</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Eleições Executivas</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>contagem acumulada de eleições para governador</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3483,6 +4008,21 @@
           <t>ob Gouverneurs- und Präsidentschaftswahlen gleichzeitig stattfanden</t>
         </is>
       </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Eleições Exec. Coincidentes com Eleições Nacionais</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Executivo</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>se as eleições para governador e presidenciais foram coincidentes</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3566,6 +4106,21 @@
           <t>die politische Ausrichtung zwischen Präsident und Gouverneur</t>
         </is>
       </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Alinhamento Político com o Governo Nacional</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Executivo</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>o alinhamento político entre o presidente e o governador</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3649,6 +4204,21 @@
           <t>ob eine vorzeitige Wahl stattfand</t>
         </is>
       </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Eleição Antecipada</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Eleições Executivas</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>se ocorreu uma eleição antecipada</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3722,6 +4292,16 @@
           <t>Datum der Gouverneurswahl</t>
         </is>
       </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Data da Eleição</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>data da eleição para governador</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3805,6 +4385,21 @@
           <t>Gesamtzahl der eingetragenen Wähler für die Gouverneurswahl</t>
         </is>
       </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Eleitores Registrados</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Eleições Executivas</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>o total de eleitores registrados para a eleição ao governador</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3888,6 +4483,21 @@
           <t>Gesamtzahl der Personen, die bei der Gouverneurswahl abgestimmt haben</t>
         </is>
       </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Total de Eleitores</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Eleições Executivas</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>o total de pessoas que votaram na eleição ao governador</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3971,6 +4581,21 @@
           <t>der Prozentsatz der Wahlbeteiligung bei der Gouverneurswahl</t>
         </is>
       </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Participação Eleitoral %</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Eleições Executivas</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>o percentual de participação eleitoral na eleição ao governador</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4054,6 +4679,21 @@
           <t>die Gesamtzahl der gültigen Stimmen bei der Gouverneurswahl</t>
         </is>
       </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Votos Válidos</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Eleições Executivas</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>o total de votos válidos na eleição ao governador</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4137,6 +4777,21 @@
           <t>die gültigen Stimmen als Prozentsatz der Gesamtstimmen</t>
         </is>
       </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Votos Válidos %</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Eleições Executivas</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>os votos válidos como percentual do total de votos</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4220,6 +4875,21 @@
           <t>die Gesamtzahl der ungültigen Stimmen bei der Gouverneurswahl</t>
         </is>
       </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Votos Inválidos</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Eleições Executivas</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>o total de votos inválidos na eleição ao governador</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4303,6 +4973,21 @@
           <t>die ungültigen Stimmen als Prozentsatz der Gesamtstimmen</t>
         </is>
       </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Votos Inválidos %</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Eleições Executivas</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>os votos inválidos como percentual do total de votos</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4386,6 +5071,21 @@
           <t>die Gesamtstimmen des Gewinners</t>
         </is>
       </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Votos do Vencedor</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Eleições Executivas</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>o total de votos do candidato vencedor</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4469,6 +5169,21 @@
           <t>der Stimmanteil des Gewinners</t>
         </is>
       </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Votos do Vencedor %</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Eleições Executivas</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>o percentual de votos do candidato vencedor</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4552,6 +5267,21 @@
           <t>die Gesamtstimmen des Zweitplatzierten</t>
         </is>
       </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Votos do Segundo Lugar</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Eleições Executivas</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>o total de votos do candidato em segundo lugar</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4635,6 +5365,21 @@
           <t>der Stimmanteil des Zweitplatzierten</t>
         </is>
       </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Votos do Segundo Lugar %</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Eleições Executivas</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>o percentual de votos do candidato em segundo lugar</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4718,6 +5463,21 @@
           <t>die Gesamtstimmen des Letztplatzierten</t>
         </is>
       </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Votos do Último Lugar</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Eleições Executivas</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>o total de votos do candidato em último lugar</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4801,6 +5561,21 @@
           <t>der Stimmanteil des Letztplatzierten</t>
         </is>
       </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Votos do Último Lugar %</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Eleições Executivas</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>o percentual de votos do candidato em último lugar</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4884,6 +5659,21 @@
           <t>die Differenz in Stimmprozenten zwischen Gewinner und Zweitem</t>
         </is>
       </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Margem de Vitória</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Eleições Executivas</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>a diferença em percentual de votos entre o vencedor e o segundo lugar</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4967,6 +5757,21 @@
           <t>die Anzahl der an der Wahl teilnehmenden Parteien</t>
         </is>
       </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Número de Partidos</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Eleições Executivas</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>o número de partidos que concorrem na eleição</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5045,6 +5850,21 @@
           <t>gibt an, in welcher Kammer die Wahlen stattfanden</t>
         </is>
       </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Eleição por Câmara</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Eleições Legislativas</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>indica a câmara onde foram realizadas as eleições</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5128,6 +5948,21 @@
           <t>die effektive Anzahl der Parteien (Laakso &amp; Taagepera, 1979) im Legislativbereich</t>
         </is>
       </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Número Efetivo de Partidos Leg.</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Eleições Legislativas</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>o número efetivo de partidos (Laakso e Taagepera, 1979) no Legislativo</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5211,6 +6046,21 @@
           <t>die Gesamtzahl der eingetragenen Wähler bei Legislativwahlen</t>
         </is>
       </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Eleitores Registrados Leg.</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Eleições Legislativas</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>o total de eleitores registrados nas eleições legislativas</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5294,6 +6144,21 @@
           <t>die Gesamtzahl der Wähler bei Legislativwahlen</t>
         </is>
       </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Total de Eleitores Leg.</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Eleições Legislativas</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>o total de eleitores nas eleições legislativas</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5377,6 +6242,21 @@
           <t>die Wahlbeteiligungsrate</t>
         </is>
       </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Participação Eleitoral Leg. %</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Eleições Legislativas</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>a taxa de participação eleitoral</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5460,6 +6340,21 @@
           <t>die Gesamtzahl der gültigen Stimmen</t>
         </is>
       </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Votos Válidos Leg.</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Eleições Legislativas</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>o total de votos válidos</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5543,6 +6438,21 @@
           <t>die gültigen Stimmen als Prozentsatz</t>
         </is>
       </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Votos Válidos Leg. %</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Eleições Legislativas</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>os votos válidos como % do total</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5621,6 +6531,21 @@
           <t>Name der Partei oder Koalition</t>
         </is>
       </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Nome do Partido Leg.</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Eleições Legislativas</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>nome do partido ou coalizão</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5704,6 +6629,21 @@
           <t>leere Stimmen</t>
         </is>
       </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Votos em Branco Leg.</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Eleições Legislativas</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>votos em branco</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5787,6 +6727,21 @@
           <t>nichtige Stimmen</t>
         </is>
       </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Votos Nulos Leg.</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Eleições Legislativas</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>votos nulos</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5870,6 +6825,21 @@
           <t>angefochtene Stimmen</t>
         </is>
       </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Votos Contestados Leg.</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Eleições Legislativas</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>votos contestados</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5953,6 +6923,21 @@
           <t>Stimmen korrigiert wegen Protokolldiskrepanz</t>
         </is>
       </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Votos por Discrepância de Ata Leg.</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Eleições Legislativas</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>votos ajustados por discrepância na ata</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6036,6 +7021,21 @@
           <t>Marge zwischen Gewinner und Zweitem</t>
         </is>
       </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Margem de Vitória Leg. %</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Eleições Legislativas</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>margem entre vencedor e segundo lugar</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
@@ -6119,6 +7119,21 @@
           <t>kumulierte Anzahl von Legislativwahlen</t>
         </is>
       </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Eleições Acumuladas Leg.</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Eleições Legislativas</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>a contagem acumulada de eleições legislativas</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6202,6 +7217,21 @@
           <t>ob Legislativ- und Präsidentschaftswahlen im selben Jahr stattfanden</t>
         </is>
       </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Eleições Leg. Coincidentes com Eleições Nacionais</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Eleições Legislativas</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>se as eleições legislativas e presidenciais ocorreram no mesmo ano</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6285,6 +7315,21 @@
           <t>die an der Wahl teilnehmenden Parteien</t>
         </is>
       </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Número de Partidos Leg.</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Eleições Legislativas</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>os partidos que concorrem na eleição</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6368,6 +7413,21 @@
           <t>die Gesamtzahl der zu besetzenden Sitze</t>
         </is>
       </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Cadeiras em Disputa Leg.</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Eleições Legislativas</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>o total de cadeiras em disputa</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6451,6 +7511,21 @@
           <t>die Gesamtzahl der Sitze in der Legislative</t>
         </is>
       </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Total de Cadeiras da Câmara Leg.</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Eleições Legislativas</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>o total de cadeiras na legislatura</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6534,6 +7609,21 @@
           <t>Sitze der Gouverneurspartei</t>
         </is>
       </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Cadeiras do Partido Governante Leg.</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Eleições Legislativas</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>cadeiras do partido do governador</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6617,6 +7707,21 @@
           <t>Prozentsatz der Sitze der Gouverneurspartei</t>
         </is>
       </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Cadeiras do Partido Governante Leg. %</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Eleições Legislativas</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>percentual de cadeiras do partido do governador</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6700,6 +7805,21 @@
           <t>Sitze der Oppositionsparteien</t>
         </is>
       </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Cadeiras da Oposição Leg.</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Eleições Legislativas</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>cadeiras dos partidos de oposição</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6783,6 +7903,21 @@
           <t>Prozentsatz der Oppositionssitze</t>
         </is>
       </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Cadeiras da Oposição Leg. %</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Eleições Legislativas</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>percentual de cadeiras da oposição</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6866,6 +8001,21 @@
           <t>Anzahl der Gesetzgebungskammern</t>
         </is>
       </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Tipo de Câmara</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Eleições Legislativas</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>o número de câmaras legislativas</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6949,6 +8099,21 @@
           <t>Dauer des legislativen Mandats in Jahren</t>
         </is>
       </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Duração do Mandato Leg.</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Eleições Legislativas</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>a duração do mandato legislativo em anos</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7032,6 +8197,21 @@
           <t>die Art der Kammererneuerung</t>
         </is>
       </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Tipo de Renovação Leg.</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Eleições Legislativas</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>o tipo de renovação da câmara</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7115,6 +8295,21 @@
           <t>das Wahlsystem der Kammer</t>
         </is>
       </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Sistema Eleitoral Leg.</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Eleições Legislativas</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>o sistema eleitoral da câmara</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7193,6 +8388,21 @@
           <t>von einer Partei gewonnene Sitze</t>
         </is>
       </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Cadeiras do Partido</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Eleições Legislativas</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>cadeiras conquistadas por um partido</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7271,6 +8481,21 @@
           <t>Gesamtstimmen für eine Partei oder Koalition</t>
         </is>
       </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Votos do Partido Leg.</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Eleições Legislativas</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>total de votos para um partido ou coalizão</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7349,6 +8574,21 @@
           <t>Stimmen mit strittiger Zuordnung</t>
         </is>
       </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Votos Disputados Leg.</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Eleições Legislativas</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>votos com identidade disputada</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7427,6 +8667,21 @@
           <t>Datum der subnationalen Legislativwahlen</t>
         </is>
       </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Data da Eleição Leg.</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Eleições Legislativas</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>data das eleições legislativas subnacionais</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7505,6 +8760,21 @@
           <t>Stimmanteil der Partei</t>
         </is>
       </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Votos do Partido Leg. %</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Eleições Legislativas</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>percentual de votos do partido</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7583,6 +8853,21 @@
           <t>Sitze als Prozentsatz der Gesamtsitze</t>
         </is>
       </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Cadeiras do Partido %</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Eleições Legislativas</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>cadeiras como % do total em disputa</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7661,6 +8946,21 @@
           <t>Startdatum des Mandats des nationalen Exekutivchefs</t>
         </is>
       </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Data de Início (Executivo Nacional)</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Executivo</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>data de início do mandato do executivo nacional</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7739,6 +9039,21 @@
           <t>Enddatum des Mandats des nationalen Exekutivchefs</t>
         </is>
       </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Data de Fim (Executivo Nacional)</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Executivo</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>data de fim do mandato do executivo nacional</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7817,6 +9132,21 @@
           <t>kumulierte Amtsjahre des nationalen Staatsoberhauptes</t>
         </is>
       </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Anos Acumulados no Poder (Nacional)</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Executivo</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>anos acumulados do chefe de estado nacional no poder</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7895,6 +9225,21 @@
           <t>Startdatum des Mandats des subnationalen Exekutivchefs</t>
         </is>
       </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Data de Início (Executivo Subnacional)</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Executivo</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>data de início do mandato do executivo subnacional</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7973,6 +9318,21 @@
           <t>Enddatum des Mandats des subnationalen Exekutivchefs</t>
         </is>
       </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Data de Fim (Executivo Subnacional)</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Executivo</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>data de fim do mandato do executivo subnacional</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -8051,6 +9411,21 @@
           <t>ob eine Exekutivwahl in diesem Jahr stattfand (1=ja)</t>
         </is>
       </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Eleição Ocorrida</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Eleições Executivas</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>se ocorreu uma eleição executiva naquele ano (1=sim)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -8129,6 +9504,21 @@
           <t>Name des Gouverneurs-Gewinners</t>
         </is>
       </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Candidato Vencedor</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Eleições Executivas</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>nome do candidato vencedor ao governo</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -8207,6 +9597,21 @@
           <t>Datum der subnationalen Exekutivwahl</t>
         </is>
       </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Data da Eleição (Executiva)</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Eleições Executivas</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>data da eleição executiva subnacional</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -8283,6 +9688,21 @@
       <c r="S97" t="inlineStr">
         <is>
           <t>kumulierte Anzahl subnationaler Exekutivwahlen in einem Staat</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Eleições Acumuladas</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Eleições Executivas</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>contagem acumulada de eleições executivas subnacionais em um estado</t>
         </is>
       </c>
     </row>
